--- a/Plan de Mejoramiento MCIC Investigacion.xlsx
+++ b/Plan de Mejoramiento MCIC Investigacion.xlsx
@@ -3169,7 +3169,7 @@
       </c>
       <c r="X14" s="102" t="inlineStr">
         <is>
-          <t>El 36% de los profesores del programa (4 de 11, según Cuadro Maestro CNA) han completado o cursado y aprobado capacitación docente (SCRUM y/o ILUD), superando la meta del 15%.</t>
+          <t>El 48% de los profesores del programa (15 de 31, según el listado de la Decanatura) han realizado capacitación docente (SCRUM, ILUD u otras capacitaciones con certificado), superando la meta del 15%.</t>
         </is>
       </c>
       <c r="Y14" s="80" t="inlineStr">
